--- a/LubanTmpl/Datas/__beans__.xlsx
+++ b/LubanTmpl/Datas/__beans__.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29413"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30313"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\Thirds\XIHFrameWork\LubanTmpl\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B087C43-0ED9-42D1-AD41-97A027BDDA3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A9814ED-799E-4076-871A-057B8B639CDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28275" yWindow="915" windowWidth="25695" windowHeight="14190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1035" yWindow="1275" windowWidth="28830" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="31">
   <si>
     <t>##var</t>
   </si>
@@ -98,6 +98,24 @@
   <si>
     <t>别名</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>RewardItem</t>
+  </si>
+  <si>
+    <t>;:,</t>
+  </si>
+  <si>
+    <t>itemType</t>
+  </si>
+  <si>
+    <t>ItemEnum</t>
+  </si>
+  <si>
+    <t>num</t>
+  </si>
+  <si>
+    <t>int</t>
   </si>
 </sst>
 </file>
@@ -182,15 +200,21 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
@@ -472,7 +496,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P3"/>
+  <dimension ref="A1:P5"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="4" width="20.625" customWidth="1"/>
@@ -510,15 +534,15 @@
       <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-      <c r="O1" s="2"/>
-      <c r="P1" s="2"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
+      <c r="N1" s="3"/>
+      <c r="O1" s="3"/>
+      <c r="P1" s="3"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
@@ -527,7 +551,7 @@
       <c r="J2" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="K2" s="2" t="s">
         <v>19</v>
       </c>
       <c r="L2" t="s">
@@ -542,7 +566,7 @@
       <c r="O2" t="s">
         <v>8</v>
       </c>
-      <c r="P2" s="3" t="s">
+      <c r="P2" s="2" t="s">
         <v>20</v>
       </c>
     </row>
@@ -568,7 +592,7 @@
       <c r="J3" t="s">
         <v>15</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="K3" s="2" t="s">
         <v>24</v>
       </c>
       <c r="L3" t="s">
@@ -580,6 +604,48 @@
       <c r="N3" t="s">
         <v>18</v>
       </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="B4" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="M4" s="4"/>
+      <c r="N4" s="4"/>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="K5" s="4"/>
+      <c r="L5" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="M5" s="4"/>
+      <c r="N5" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="1">
